--- a/diseases/d098/2010-2014.xlsx
+++ b/diseases/d098/2010-2014.xlsx
@@ -1292,17 +1292,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>US-DE</t>
+          <t>US-GA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Delaware, United States</t>
+          <t>Georgia, United States</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1336,102 +1336,24 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>HOLD_US_0bb42b8b2dac52fb926121a619f2</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Ehrlichiosis/Anaplasmosis†, Ehrlichia chaffeensis</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Ehrlichiosis/Anaplasmosis†, Ehrlichia chaffeensis</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>country:US-DE:national</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN6" t="b">
-        <v>0</v>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1439,31 +1361,16 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>HOLD_US_3f0d119ee47aa9a2296aeeb57893</t>
+          <t>HOLD_US_0bb42b8b2dac52fb926121a619f2</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1534,12 +1441,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>US-GA</t>
+          <t>US-KS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Georgia, United States</t>
+          <t>Kansas, United States</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1564,7 +1471,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2014-07-12</t>
+          <t>2014-07-26</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1573,13 +1480,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1673,17 +1580,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>US-DE</t>
+          <t>US-GA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Delaware, United States</t>
+          <t>Georgia, United States</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1708,12 +1615,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2014-07-26</t>
+          <t>2014-08-09</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2014-07</t>
+          <t>2014-08</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1730,89 +1637,11 @@
           <t>HOLD_US_0bb42b8b2dac52fb926121a619f2</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Ehrlichiosis/Anaplasmosis†, Ehrlichia chaffeensis</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Ehrlichiosis/Anaplasmosis†, Ehrlichia chaffeensis</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>country:US-DE:national</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN8" t="b">
-        <v>0</v>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1820,31 +1649,16 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>HOLD_US_3f0d119ee47aa9a2296aeeb57893</t>
+          <t>HOLD_US_0bb42b8b2dac52fb926121a619f2</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1915,12 +1729,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>US-KS</t>
+          <t>US-WV</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Kansas, United States</t>
+          <t>West Virginia, United States</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1945,12 +1759,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2014-07-26</t>
+          <t>2014-08-09</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2014-07</t>
+          <t>2014-08</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -2054,17 +1868,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>US-DE</t>
+          <t>US-SC</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Delaware, United States</t>
+          <t>South Carolina, United States</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2089,7 +1903,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2014-08-09</t>
+          <t>2014-08-16</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -2098,102 +1912,24 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>HOLD_US_0bb42b8b2dac52fb926121a619f2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Ehrlichiosis/Anaplasmosis†, Ehrlichia chaffeensis</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>Ehrlichiosis/Anaplasmosis†, Ehrlichia chaffeensis</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>country:US-DE:national</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN10" t="b">
-        <v>0</v>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -2201,31 +1937,16 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>HOLD_US_3f0d119ee47aa9a2296aeeb57893</t>
+          <t>HOLD_US_0bb42b8b2dac52fb926121a619f2</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2296,12 +2017,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>US-GA</t>
+          <t>US-WV</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Georgia, United States</t>
+          <t>West Virginia, United States</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2326,12 +2047,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2014-08-09</t>
+          <t>2014-10-25</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2014-10</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2407,1386 +2128,6 @@
         </is>
       </c>
       <c r="BC11" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>D098</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>ehrlichiosis-and-anaplasmosis</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Ehrlichiosis and Anaplasmosis</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>US-WV</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>West Virginia, United States</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>D098</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Ehrlichiosis and Anaplasmosis</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>埃立克体病和无形体病</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>2014-08-09</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>HOLD_US_0bb42b8b2dac52fb926121a619f2</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>HOLD_US_0bb42b8b2dac52fb926121a619f2</t>
-        </is>
-      </c>
-      <c r="AT12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>D098</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>ehrlichiosis-and-anaplasmosis</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Ehrlichiosis and Anaplasmosis</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>US-DE</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Delaware, United States</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>D098</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Ehrlichiosis and Anaplasmosis</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>埃立克体病和无形体病</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>2014-08-16</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>HOLD_US_0bb42b8b2dac52fb926121a619f2</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Ehrlichiosis/Anaplasmosis†, Ehrlichia chaffeensis</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>Ehrlichiosis/Anaplasmosis†, Ehrlichia chaffeensis</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>country:US-DE:national</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>HOLD_US_3f0d119ee47aa9a2296aeeb57893</t>
-        </is>
-      </c>
-      <c r="AT13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>D098</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>ehrlichiosis-and-anaplasmosis</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Ehrlichiosis and Anaplasmosis</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>US-SC</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>South Carolina, United States</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>D098</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Ehrlichiosis and Anaplasmosis</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>埃立克体病和无形体病</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>2014-08-16</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="N14" t="n">
-        <v>2</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>HOLD_US_0bb42b8b2dac52fb926121a619f2</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>HOLD_US_0bb42b8b2dac52fb926121a619f2</t>
-        </is>
-      </c>
-      <c r="AT14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>D098</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>ehrlichiosis-and-anaplasmosis</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Ehrlichiosis and Anaplasmosis</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>US-DE</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Delaware, United States</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>D098</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Ehrlichiosis and Anaplasmosis</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>埃立克体病和无形体病</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>2014-08-23</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>HOLD_US_0bb42b8b2dac52fb926121a619f2</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Ehrlichiosis/Anaplasmosis†, Ehrlichia chaffeensis</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>Ehrlichiosis/Anaplasmosis†, Ehrlichia chaffeensis</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>country:US-DE:national</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>HOLD_US_3f0d119ee47aa9a2296aeeb57893</t>
-        </is>
-      </c>
-      <c r="AT15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>D098</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ehrlichiosis-and-anaplasmosis</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Ehrlichiosis and Anaplasmosis</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>US-DE</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Delaware, United States</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>D098</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Ehrlichiosis and Anaplasmosis</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>埃立克体病和无形体病</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>2014-08-23</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>HOLD_US_e270eb874e8c48b9726507b457d1</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Ehrlichiosis/Anaplasmosis†, Anaplasma phagocytophilum</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>Ehrlichiosis/Anaplasmosis†, Anaplasma phagocytophilum</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>country:US-DE:national</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>HOLD_US_3f0d119ee47aa9a2296aeeb57893</t>
-        </is>
-      </c>
-      <c r="AT16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="BC16" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>D098</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>ehrlichiosis-and-anaplasmosis</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Ehrlichiosis and Anaplasmosis</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>US-WV</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>West Virginia, United States</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>D098</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Ehrlichiosis and Anaplasmosis</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>埃立克体病和无形体病</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>2014-10-25</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2014-10</t>
-        </is>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>HOLD_US_0bb42b8b2dac52fb926121a619f2</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>HOLD_US_0bb42b8b2dac52fb926121a619f2</t>
-        </is>
-      </c>
-      <c r="AT17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>D098</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>ehrlichiosis-and-anaplasmosis</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Ehrlichiosis and Anaplasmosis</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>US-DE</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Delaware, United States</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>D098</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Ehrlichiosis and Anaplasmosis</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>埃立克体病和无形体病</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>2014-11-01</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2014-11</t>
-        </is>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>HOLD_US_0bb42b8b2dac52fb926121a619f2</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Ehrlichiosis/Anaplasmosis†, Ehrlichia chaffeensis</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>Ehrlichiosis/Anaplasmosis†, Ehrlichia chaffeensis</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>country:US-DE:national</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>HOLD_US_3f0d119ee47aa9a2296aeeb57893</t>
-        </is>
-      </c>
-      <c r="AT18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
-      </c>
-      <c r="AV18" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="BA18" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="BC18" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -3825,7 +2166,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2014-11-01</t>
+          <t>2014-10-25</t>
         </is>
       </c>
     </row>
@@ -3918,7 +2259,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -3938,7 +2279,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3948,7 +2289,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
